--- a/Data/Building/MeetingRoomOne.Brightness.xlsx
+++ b/Data/Building/MeetingRoomOne.Brightness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H426"/>
+  <dimension ref="A1:I402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709255950</v>
+        <v>1711847157</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709255974</v>
+        <v>1711847180</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709255988</v>
+        <v>1711847202</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709258868</v>
+        <v>1711850459</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709258904</v>
+        <v>1711850481</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709258927</v>
+        <v>1711850507</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709258956</v>
+        <v>1711850543</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709258990</v>
+        <v>1711850565</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709259025</v>
+        <v>1711850610</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709263025</v>
+        <v>1711850655</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709263059</v>
+        <v>1711852620</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709263085</v>
+        <v>1711852645</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709263122</v>
+        <v>1711852682</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709263165</v>
+        <v>1711852711</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709263195</v>
+        <v>1711852737</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,11 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +991,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709269192</v>
+        <v>1711859102</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1005,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1024,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709269222</v>
+        <v>1711859121</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1038,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1057,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709269289</v>
+        <v>1711859155</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1071,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1090,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709269354</v>
+        <v>1711859188</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1104,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1123,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709269391</v>
+        <v>1711859222</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1137,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1156,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709269424</v>
+        <v>1711859257</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1170,11 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1193,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709250796</v>
+        <v>1711860801</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1207,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1226,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709250815</v>
+        <v>1711860831</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1240,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1259,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709250844</v>
+        <v>1711860855</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1273,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1292,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709251744</v>
+        <v>1711860880</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1306,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1325,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709251763</v>
+        <v>1711860911</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1358,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709251796</v>
+        <v>1711860936</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1372,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1391,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709254618</v>
+        <v>1711930459</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1405,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1424,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709254645</v>
+        <v>1711930471</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1438,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1457,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709254681</v>
+        <v>1711930508</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1471,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1490,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709258336</v>
+        <v>1711930543</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1504,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1523,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709258371</v>
+        <v>1711930583</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1537,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1556,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709258393</v>
+        <v>1711930619</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1570,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1589,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709262798</v>
+        <v>1711932542</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1603,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1622,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709262824</v>
+        <v>1711932569</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1636,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1655,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709262842</v>
+        <v>1711932598</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1669,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1688,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709262874</v>
+        <v>1711932628</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1702,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1721,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709262916</v>
+        <v>1711932674</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1735,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1754,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709262953</v>
+        <v>1711932715</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1768,11 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1791,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709339190</v>
+        <v>1711934905</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1805,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1824,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709339221</v>
+        <v>1711934951</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1838,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1857,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709339250</v>
+        <v>1711934973</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1871,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1890,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709339314</v>
+        <v>1711935003</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1904,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1923,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709339344</v>
+        <v>1711935033</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1937,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1956,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709339389</v>
+        <v>1711935088</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1970,11 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1993,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709340383</v>
+        <v>1711938888</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2007,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2026,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709340399</v>
+        <v>1711938914</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2040,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2059,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709340423</v>
+        <v>1711938948</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2073,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2092,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709340450</v>
+        <v>1711938976</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2106,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2125,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709340486</v>
+        <v>1711939016</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2139,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2158,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709340511</v>
+        <v>1711939049</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2172,11 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2195,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709346455</v>
+        <v>1712018448</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2209,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2228,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709346483</v>
+        <v>1712018489</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2242,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2261,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709346513</v>
+        <v>1712018511</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2275,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2294,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709346551</v>
+        <v>1712018538</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2308,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2327,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709346588</v>
+        <v>1712018562</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2341,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2360,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709346621</v>
+        <v>1712018592</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2374,11 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2397,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709348866</v>
+        <v>1712021146</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2411,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2430,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709348895</v>
+        <v>1712021171</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2444,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2463,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709348926</v>
+        <v>1712021192</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2477,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2496,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709348947</v>
+        <v>1712023379</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2510,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2529,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709348984</v>
+        <v>1712023420</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2543,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2562,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709349027</v>
+        <v>1712023459</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2576,11 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2599,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709425416</v>
+        <v>1712028515</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2613,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2632,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709425442</v>
+        <v>1712028544</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2646,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2665,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709425467</v>
+        <v>1712028564</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2679,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2698,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709425493</v>
+        <v>1712028584</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2712,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2731,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709425510</v>
+        <v>1712028608</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2745,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2764,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709429588</v>
+        <v>1712028647</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2778,11 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2801,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709429620</v>
+        <v>1712104358</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2815,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2834,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709429645</v>
+        <v>1712104387</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2848,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2867,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709429666</v>
+        <v>1712104421</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2881,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2900,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709429700</v>
+        <v>1712104449</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2914,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2933,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709429728</v>
+        <v>1712104474</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2947,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2966,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709429744</v>
+        <v>1712104497</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2980,11 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3003,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709431740</v>
+        <v>1712109865</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3017,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3036,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709431776</v>
+        <v>1712109884</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3050,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3069,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709431794</v>
+        <v>1712109908</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3083,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3102,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709431823</v>
+        <v>1712109931</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3116,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3135,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709431858</v>
+        <v>1712109960</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3149,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3168,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709431877</v>
+        <v>1712109985</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3182,11 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3205,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709436437</v>
+        <v>1712114470</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3219,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3238,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709436464</v>
+        <v>1712114507</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3252,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3271,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709436487</v>
+        <v>1712114533</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3285,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3304,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709436522</v>
+        <v>1712114565</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3318,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3337,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709436553</v>
+        <v>1712114585</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3351,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3370,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709436580</v>
+        <v>1712114609</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3384,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3403,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709513304</v>
+        <v>1712190472</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3417,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3436,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709513343</v>
+        <v>1712190495</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3450,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3469,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709513367</v>
+        <v>1712190520</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3483,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3502,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709513393</v>
+        <v>1712190550</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3516,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3535,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709513435</v>
+        <v>1712190575</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3549,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3568,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709513466</v>
+        <v>1712190601</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3582,11 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3605,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709521785</v>
+        <v>1712195542</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3619,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3638,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709521831</v>
+        <v>1712195569</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3652,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3671,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709521859</v>
+        <v>1712195596</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3685,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3704,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709521889</v>
+        <v>1712195632</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3718,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3737,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709521934</v>
+        <v>1712195657</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3751,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3770,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709521965</v>
+        <v>1712195684</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3784,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3803,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709602319</v>
+        <v>1712198595</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3817,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3836,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709602355</v>
+        <v>1712198614</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3850,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3869,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709602383</v>
+        <v>1712198633</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3883,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3902,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709602419</v>
+        <v>1712198657</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3916,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3935,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709602458</v>
+        <v>1712198687</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3949,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3968,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709602496</v>
+        <v>1712198717</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3982,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4001,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709609267</v>
+        <v>1712274790</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4015,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4034,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709609297</v>
+        <v>1712274821</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4048,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4067,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1709609338</v>
+        <v>1712274864</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4081,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4100,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1709609363</v>
+        <v>1712274896</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4114,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4133,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1709609395</v>
+        <v>1712274920</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4147,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4166,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1709609444</v>
+        <v>1712274955</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4180,11 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4203,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1709855326</v>
+        <v>1712276971</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4217,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4236,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1709855351</v>
+        <v>1712276998</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4250,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4269,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1709855386</v>
+        <v>1712277023</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4283,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4302,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1709855424</v>
+        <v>1712277050</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4316,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4335,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1709855460</v>
+        <v>1712277072</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4349,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4368,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1709855485</v>
+        <v>1712277095</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4382,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4401,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1709856532</v>
+        <v>1712285655</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4415,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4434,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1709856566</v>
+        <v>1712285680</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4448,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4467,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1709856595</v>
+        <v>1712285706</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4481,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4500,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1709856625</v>
+        <v>1712285735</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4514,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4533,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1709856661</v>
+        <v>1712285763</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4547,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4566,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1709856694</v>
+        <v>1712285793</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4580,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4599,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1709863220</v>
+        <v>1712535510</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4613,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4632,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1709863250</v>
+        <v>1712535528</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4646,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4665,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1709863287</v>
+        <v>1712535558</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4679,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4698,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1709865582</v>
+        <v>1712536918</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4712,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4731,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1709865617</v>
+        <v>1712536952</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4745,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4764,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1709865651</v>
+        <v>1712536993</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4778,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4797,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1709942617</v>
+        <v>1712540463</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4811,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4830,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1709942651</v>
+        <v>1712540493</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4844,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4863,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1709942678</v>
+        <v>1712540521</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4877,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4896,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1709942701</v>
+        <v>1712540552</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4910,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4929,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1709942726</v>
+        <v>1712540580</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4943,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4962,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1709942755</v>
+        <v>1712540604</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4976,11 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4999,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1709942776</v>
+        <v>1712546318</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5013,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5032,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1709946568</v>
+        <v>1712546334</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5046,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5065,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1709946594</v>
+        <v>1712546355</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5079,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5098,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1709946628</v>
+        <v>1712546384</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5112,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5131,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1709946660</v>
+        <v>1712546421</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5145,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5164,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1709946700</v>
+        <v>1712546443</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5178,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5197,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1709952564</v>
+        <v>1712624600</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5211,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5230,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1709952590</v>
+        <v>1712624635</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5244,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5263,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1709952619</v>
+        <v>1712624663</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5277,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5296,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1709952643</v>
+        <v>1712624687</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5310,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5329,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1709952669</v>
+        <v>1712624718</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5343,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5362,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1709952690</v>
+        <v>1712624753</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5376,11 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5399,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710029717</v>
+        <v>1712628053</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5413,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5432,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710029740</v>
+        <v>1712628074</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5446,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5465,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710029763</v>
+        <v>1712628109</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5479,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5498,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710029783</v>
+        <v>1712628148</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5512,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5531,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710029808</v>
+        <v>1712628174</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5545,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5564,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710029830</v>
+        <v>1712628204</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5578,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5597,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710035352</v>
+        <v>1712632744</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5611,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5630,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710035386</v>
+        <v>1712632766</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5644,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5663,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710035423</v>
+        <v>1712632795</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5677,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5696,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710035450</v>
+        <v>1712632822</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5710,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5729,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710035482</v>
+        <v>1712632853</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5743,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5762,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710035514</v>
+        <v>1712632894</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5776,11 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5799,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710037395</v>
+        <v>1712711915</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5813,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5832,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710037425</v>
+        <v>1712711951</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5846,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5865,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710037449</v>
+        <v>1712711984</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5879,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5898,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710037477</v>
+        <v>1712712022</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5912,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5931,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710037516</v>
+        <v>1712712061</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5945,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5964,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710037543</v>
+        <v>1712712090</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +5978,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5997,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710042725</v>
+        <v>1712713082</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6011,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6030,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710042771</v>
+        <v>1712713109</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6044,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6063,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710042797</v>
+        <v>1712713129</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6077,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6096,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710042829</v>
+        <v>1712713165</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6110,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6129,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710042859</v>
+        <v>1712713198</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6143,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6162,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710042892</v>
+        <v>1712713231</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6176,11 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6199,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710117838</v>
+        <v>1712720425</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6213,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6232,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710117874</v>
+        <v>1712720464</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6246,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6265,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710117911</v>
+        <v>1712720490</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6279,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6298,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710117939</v>
+        <v>1712720523</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6312,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6331,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710117971</v>
+        <v>1712720567</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6345,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6364,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710117997</v>
+        <v>1712720600</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6378,11 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6401,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710120514</v>
+        <v>1712799875</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6165,6 +6415,7 @@
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6434,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710120539</v>
+        <v>1712799905</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6448,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6467,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710120570</v>
+        <v>1712799933</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6481,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6500,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710120615</v>
+        <v>1712799951</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6514,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6533,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710120641</v>
+        <v>1712799988</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6547,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6566,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710120682</v>
+        <v>1712800043</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6580,11 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6603,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710128201</v>
+        <v>1712805498</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6617,7 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6636,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710128225</v>
+        <v>1712805527</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6650,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6669,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710128256</v>
+        <v>1712805553</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6683,7 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6702,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710130158</v>
+        <v>1712806027</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6453,6 +6716,7 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6735,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710130188</v>
+        <v>1712806056</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6749,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6768,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710130226</v>
+        <v>1712806097</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6782,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6801,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710203272</v>
+        <v>1712806129</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6549,6 +6815,7 @@
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6834,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710203325</v>
+        <v>1712806562</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6577,10 +6844,11 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6867,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710203361</v>
+        <v>1712806623</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6609,10 +6877,11 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6900,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710203396</v>
+        <v>1712806648</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6645,6 +6914,7 @@
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6933,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710203422</v>
+        <v>1712806668</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6673,10 +6943,11 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6966,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710203467</v>
+        <v>1712806704</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6705,10 +6976,11 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +6999,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710205469</v>
+        <v>1712806751</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +7013,7 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7032,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710205492</v>
+        <v>1712806788</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6769,10 +7042,11 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7065,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710205518</v>
+        <v>1712882513</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6801,10 +7075,11 @@
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7098,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710205543</v>
+        <v>1712882560</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7112,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7131,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710205573</v>
+        <v>1712882589</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6865,10 +7141,11 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7164,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710205601</v>
+        <v>1712882626</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6897,10 +7174,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7197,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710207275</v>
+        <v>1712882661</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6933,6 +7211,7 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7230,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710207299</v>
+        <v>1712882694</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6961,10 +7240,15 @@
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7267,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710207321</v>
+        <v>1712885502</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6993,10 +7277,11 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7300,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710207353</v>
+        <v>1712885527</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7314,7 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7333,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710207378</v>
+        <v>1712885552</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7057,10 +7343,11 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7366,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710207414</v>
+        <v>1712885582</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7089,10 +7376,11 @@
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7399,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710209835</v>
+        <v>1712885610</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7413,7 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7432,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710209861</v>
+        <v>1712885647</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7153,10 +7442,15 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7469,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710209900</v>
+        <v>1712891827</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7185,10 +7479,11 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7502,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710209943</v>
+        <v>1712891850</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7516,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7535,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710209982</v>
+        <v>1712891881</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7249,10 +7545,11 @@
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7568,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710210002</v>
+        <v>1712891912</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7281,10 +7578,11 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7601,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710214833</v>
+        <v>1712891946</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7317,6 +7615,7 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7634,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710214854</v>
+        <v>1712891978</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7345,10 +7644,15 @@
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7671,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710214872</v>
+        <v>1713138958</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7377,10 +7681,11 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7704,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710214900</v>
+        <v>1713138987</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7413,6 +7718,7 @@
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7737,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1710214925</v>
+        <v>1713139012</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7441,10 +7747,11 @@
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7770,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1710214962</v>
+        <v>1713139035</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7473,10 +7780,11 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7803,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1710462796</v>
+        <v>1713139066</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7509,6 +7817,7 @@
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7836,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1710462835</v>
+        <v>1713139110</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7537,10 +7846,11 @@
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7869,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1710462863</v>
+        <v>1713141720</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7569,10 +7879,11 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7902,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1710462898</v>
+        <v>1713141758</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7605,6 +7916,7 @@
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7935,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1710462931</v>
+        <v>1713141789</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7633,10 +7945,11 @@
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +7968,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1710462966</v>
+        <v>1713141825</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7665,10 +7978,11 @@
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +8001,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1710464750</v>
+        <v>1713141869</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7701,6 +8015,7 @@
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +8034,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1710464811</v>
+        <v>1713141912</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7729,10 +8044,15 @@
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +8071,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1710464830</v>
+        <v>1713150957</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7761,10 +8081,11 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8104,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1710464860</v>
+        <v>1713150980</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7797,6 +8118,7 @@
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8137,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1710464902</v>
+        <v>1713151005</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7825,10 +8147,11 @@
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8170,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1710464951</v>
+        <v>1713151032</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7857,10 +8180,11 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8203,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1710467561</v>
+        <v>1713151059</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7893,6 +8217,7 @@
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8236,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1710467591</v>
+        <v>1713151116</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7921,10 +8246,15 @@
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8273,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1710467608</v>
+        <v>1713225262</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7953,10 +8283,11 @@
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8306,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1710467643</v>
+        <v>1713225278</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7989,6 +8320,7 @@
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8339,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1710467686</v>
+        <v>1713225294</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8017,10 +8349,11 @@
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8372,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1710467728</v>
+        <v>1713225541</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8049,10 +8382,11 @@
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8405,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1710470232</v>
+        <v>1713225564</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8085,6 +8419,7 @@
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8438,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1710470264</v>
+        <v>1713225586</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8113,10 +8448,11 @@
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
+          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8471,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1710470285</v>
+        <v>1713227742</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8145,10 +8481,11 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
+          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8504,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1710470329</v>
+        <v>1713227765</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8181,6 +8518,7 @@
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8537,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1710470353</v>
+        <v>1713227789</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8209,10 +8547,11 @@
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
+          <t>MeetingRoomOne.Brightness.state: Dark</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8570,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1710470388</v>
+        <v>1713227830</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8241,10 +8580,11 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
+          <t>MeetingRoomOne.Brightness.state: Dim</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8603,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1710470418</v>
+        <v>1713227863</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8277,6 +8617,7 @@
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8636,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1710472745</v>
+        <v>1713227891</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8309,6 +8650,11 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8673,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1710472796</v>
+        <v>1713234493</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8341,6 +8687,7 @@
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8359,7 +8706,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1710472832</v>
+        <v>1713234524</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8373,6 +8720,7 @@
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8391,7 +8739,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1710472873</v>
+        <v>1713234553</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8405,6 +8753,7 @@
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8423,7 +8772,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1710472912</v>
+        <v>1713234583</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8437,6 +8786,7 @@
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8455,7 +8805,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1710472939</v>
+        <v>1713234620</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8469,6 +8819,7 @@
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8487,7 +8838,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1710472977</v>
+        <v>1713234650</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8501,6 +8852,11 @@
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8519,7 +8875,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1710548526</v>
+        <v>1713313615</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8533,6 +8889,7 @@
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8551,7 +8908,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1710548568</v>
+        <v>1713313653</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8565,6 +8922,7 @@
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8583,7 +8941,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1710548608</v>
+        <v>1713313675</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8597,6 +8955,7 @@
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8615,7 +8974,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1710548666</v>
+        <v>1713313709</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8629,6 +8988,7 @@
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8647,7 +9007,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1710548714</v>
+        <v>1713313750</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8661,6 +9021,7 @@
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8679,7 +9040,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1710549828</v>
+        <v>1713313793</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8693,6 +9054,7 @@
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8711,7 +9073,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1710549865</v>
+        <v>1713314307</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8725,6 +9087,7 @@
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8743,7 +9106,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1710549895</v>
+        <v>1713314347</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8757,6 +9120,7 @@
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8775,7 +9139,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1710549923</v>
+        <v>1713314378</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8789,6 +9153,7 @@
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8807,7 +9172,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1710549970</v>
+        <v>1713314408</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8821,6 +9186,7 @@
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8839,7 +9205,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1710549997</v>
+        <v>1713314455</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8853,6 +9219,7 @@
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8871,7 +9238,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1710550021</v>
+        <v>1713314514</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8885,6 +9252,7 @@
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8903,7 +9271,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1710555345</v>
+        <v>1713321002</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8917,6 +9285,7 @@
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8935,7 +9304,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1710555372</v>
+        <v>1713321031</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8949,6 +9318,7 @@
         </is>
       </c>
       <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8967,7 +9337,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1710555400</v>
+        <v>1713321052</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8981,6 +9351,7 @@
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8999,7 +9370,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1710555485</v>
+        <v>1713321083</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -9013,6 +9384,7 @@
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9031,7 +9403,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1710555509</v>
+        <v>1713321130</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -9045,6 +9417,7 @@
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9063,7 +9436,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1710555533</v>
+        <v>1713321165</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -9077,6 +9450,7 @@
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9095,7 +9469,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1710559697</v>
+        <v>1713399698</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -9109,6 +9483,7 @@
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9127,7 +9502,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1710559720</v>
+        <v>1713399735</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -9141,6 +9516,7 @@
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9159,7 +9535,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1710559758</v>
+        <v>1713399757</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -9173,6 +9549,7 @@
         </is>
       </c>
       <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9191,7 +9568,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1710559786</v>
+        <v>1713399789</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -9205,6 +9582,7 @@
         </is>
       </c>
       <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9223,7 +9601,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1710559810</v>
+        <v>1713399825</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -9237,6 +9615,7 @@
         </is>
       </c>
       <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9255,7 +9634,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1710559838</v>
+        <v>1713399854</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -9269,6 +9648,11 @@
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9287,7 +9671,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1710637072</v>
+        <v>1713406375</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -9301,6 +9685,7 @@
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9319,7 +9704,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1710637094</v>
+        <v>1713406406</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -9333,6 +9718,7 @@
         </is>
       </c>
       <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9351,7 +9737,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1710637133</v>
+        <v>1713406444</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -9365,6 +9751,7 @@
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9383,7 +9770,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1710637160</v>
+        <v>1713406489</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -9397,6 +9784,7 @@
         </is>
       </c>
       <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9415,7 +9803,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1710637196</v>
+        <v>1713406521</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -9429,6 +9817,7 @@
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9447,7 +9836,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1710637230</v>
+        <v>1713406558</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -9461,6 +9850,11 @@
         </is>
       </c>
       <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9479,7 +9873,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1710641692</v>
+        <v>1713486216</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -9493,6 +9887,7 @@
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9511,7 +9906,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1710641730</v>
+        <v>1713486251</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -9525,6 +9920,7 @@
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9543,7 +9939,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1710641754</v>
+        <v>1713486275</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -9557,6 +9953,7 @@
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9575,7 +9972,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1710641778</v>
+        <v>1713488157</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -9589,6 +9986,7 @@
         </is>
       </c>
       <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9607,7 +10005,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1710641808</v>
+        <v>1713488175</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -9621,6 +10019,7 @@
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9639,7 +10038,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1710641843</v>
+        <v>1713488216</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9653,6 +10052,7 @@
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9671,7 +10071,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1710645028</v>
+        <v>1713488251</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -9685,6 +10085,7 @@
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9703,7 +10104,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1710645074</v>
+        <v>1713488282</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9717,6 +10118,7 @@
         </is>
       </c>
       <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9735,7 +10137,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1710645106</v>
+        <v>1713488310</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9749,6 +10151,7 @@
         </is>
       </c>
       <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9767,7 +10170,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1710645145</v>
+        <v>1713488348</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9781,6 +10184,7 @@
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9799,7 +10203,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1710645183</v>
+        <v>1713488395</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9813,6 +10217,7 @@
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9831,7 +10236,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1710645227</v>
+        <v>1713488422</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9845,6 +10250,7 @@
         </is>
       </c>
       <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9863,7 +10269,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1710723947</v>
+        <v>1713495325</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9877,6 +10283,7 @@
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9895,7 +10302,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1710723975</v>
+        <v>1713495362</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9909,6 +10316,7 @@
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9927,7 +10335,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1710724007</v>
+        <v>1713495387</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9941,6 +10349,7 @@
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9959,7 +10368,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1710724061</v>
+        <v>1713495435</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9973,6 +10382,7 @@
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9991,7 +10401,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1710724104</v>
+        <v>1713495475</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -10005,6 +10415,7 @@
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10023,7 +10434,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1710724136</v>
+        <v>1713495522</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -10037,6 +10448,11 @@
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10055,7 +10471,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1710728942</v>
+        <v>1713743208</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -10069,6 +10485,7 @@
         </is>
       </c>
       <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10087,7 +10504,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1710728990</v>
+        <v>1713743233</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -10101,6 +10518,7 @@
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10119,7 +10537,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1710729023</v>
+        <v>1713743254</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -10133,6 +10551,7 @@
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10151,7 +10570,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1710729418</v>
+        <v>1713743288</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -10165,6 +10584,7 @@
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10183,7 +10603,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1710729452</v>
+        <v>1713743332</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -10197,6 +10617,7 @@
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10215,7 +10636,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1710729471</v>
+        <v>1713743377</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -10229,6 +10650,11 @@
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10247,7 +10673,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1710731964</v>
+        <v>1713748975</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -10261,6 +10687,7 @@
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10279,7 +10706,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1710732000</v>
+        <v>1713749018</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -10293,6 +10720,7 @@
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10311,7 +10739,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1710732030</v>
+        <v>1713749052</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -10325,6 +10753,7 @@
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10343,7 +10772,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1710732064</v>
+        <v>1713749082</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -10357,6 +10786,7 @@
         </is>
       </c>
       <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10375,7 +10805,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1710732096</v>
+        <v>1713749114</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -10389,6 +10819,7 @@
         </is>
       </c>
       <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10407,7 +10838,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1710732128</v>
+        <v>1713749147</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -10421,6 +10852,11 @@
         </is>
       </c>
       <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10439,7 +10875,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1710808080</v>
+        <v>1713753085</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -10453,6 +10889,7 @@
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10471,7 +10908,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1710808116</v>
+        <v>1713753126</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -10485,6 +10922,7 @@
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10503,7 +10941,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1710808140</v>
+        <v>1713753155</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -10517,6 +10955,7 @@
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10535,7 +10974,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1710808168</v>
+        <v>1713753191</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -10549,6 +10988,7 @@
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10567,7 +11007,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1710808195</v>
+        <v>1713753224</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -10581,6 +11021,7 @@
         </is>
       </c>
       <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10599,7 +11040,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1710808232</v>
+        <v>1713753267</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -10613,6 +11054,11 @@
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10631,7 +11077,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1710811873</v>
+        <v>1713832464</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -10645,6 +11091,7 @@
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10663,7 +11110,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1710811920</v>
+        <v>1713832489</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -10677,6 +11124,7 @@
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10695,7 +11143,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1710811949</v>
+        <v>1713832516</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -10709,6 +11157,7 @@
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10727,7 +11176,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1710811991</v>
+        <v>1713832556</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -10741,6 +11190,7 @@
         </is>
       </c>
       <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10759,7 +11209,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1710812019</v>
+        <v>1713832583</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10773,6 +11223,7 @@
         </is>
       </c>
       <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10791,7 +11242,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1710812050</v>
+        <v>1713832608</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10805,6 +11256,7 @@
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -10823,7 +11275,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1710817601</v>
+        <v>1713835353</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -10837,6 +11289,7 @@
         </is>
       </c>
       <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10855,7 +11308,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1710817648</v>
+        <v>1713835390</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -10869,6 +11322,7 @@
         </is>
       </c>
       <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10887,7 +11341,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1710817673</v>
+        <v>1713835414</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -10901,6 +11355,7 @@
         </is>
       </c>
       <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10919,7 +11374,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1710817704</v>
+        <v>1713835437</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -10933,6 +11388,7 @@
         </is>
       </c>
       <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10951,7 +11407,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1710817726</v>
+        <v>1713835475</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10965,6 +11421,7 @@
         </is>
       </c>
       <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10983,7 +11440,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1710817753</v>
+        <v>1713835506</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10997,6 +11454,11 @@
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11015,7 +11477,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1711068289</v>
+        <v>1713840075</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -11029,6 +11491,7 @@
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11047,7 +11510,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1711068322</v>
+        <v>1713840110</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -11061,6 +11524,7 @@
         </is>
       </c>
       <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11079,7 +11543,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1711068354</v>
+        <v>1713840144</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -11093,6 +11557,7 @@
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11111,7 +11576,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1711068396</v>
+        <v>1713840173</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -11125,6 +11590,7 @@
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11143,7 +11609,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1711068422</v>
+        <v>1713840202</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -11157,6 +11623,7 @@
         </is>
       </c>
       <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11175,7 +11642,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1711068445</v>
+        <v>1713840232</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -11189,6 +11656,11 @@
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11207,7 +11679,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1711074680</v>
+        <v>1713844335</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -11221,6 +11693,7 @@
         </is>
       </c>
       <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11239,7 +11712,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1711074721</v>
+        <v>1713844365</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -11253,6 +11726,7 @@
         </is>
       </c>
       <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11271,7 +11745,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1711074751</v>
+        <v>1713844391</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -11285,6 +11759,7 @@
         </is>
       </c>
       <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11303,7 +11778,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1711074797</v>
+        <v>1713844407</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -11317,6 +11792,7 @@
         </is>
       </c>
       <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11335,7 +11811,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1711074825</v>
+        <v>1713844430</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -11349,6 +11825,7 @@
         </is>
       </c>
       <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11367,7 +11844,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1711074855</v>
+        <v>1713844455</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -11381,6 +11858,11 @@
         </is>
       </c>
       <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11399,7 +11881,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1711152715</v>
+        <v>1713920058</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -11413,6 +11895,7 @@
         </is>
       </c>
       <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11431,7 +11914,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1711152745</v>
+        <v>1713920076</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -11445,6 +11928,7 @@
         </is>
       </c>
       <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11463,7 +11947,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1711152764</v>
+        <v>1713920097</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -11477,6 +11961,7 @@
         </is>
       </c>
       <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11495,7 +11980,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1711152794</v>
+        <v>1713920122</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -11509,6 +11994,7 @@
         </is>
       </c>
       <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11527,7 +12013,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1711152824</v>
+        <v>1713920152</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -11541,6 +12027,7 @@
         </is>
       </c>
       <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11559,7 +12046,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1711152854</v>
+        <v>1713920187</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -11573,6 +12060,11 @@
         </is>
       </c>
       <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11591,7 +12083,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1711154895</v>
+        <v>1713924781</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -11605,6 +12097,7 @@
         </is>
       </c>
       <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11623,7 +12116,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1711154923</v>
+        <v>1713924802</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -11637,6 +12130,7 @@
         </is>
       </c>
       <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -11655,7 +12149,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1711154952</v>
+        <v>1713924829</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -11669,6 +12163,7 @@
         </is>
       </c>
       <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -11687,7 +12182,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1711160444</v>
+        <v>1713924857</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -11701,6 +12196,7 @@
         </is>
       </c>
       <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11719,7 +12215,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1711160470</v>
+        <v>1713924881</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -11733,6 +12229,7 @@
         </is>
       </c>
       <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11751,7 +12248,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1711160497</v>
+        <v>1713924912</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -11765,6 +12262,11 @@
         </is>
       </c>
       <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11783,7 +12285,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1711163374</v>
+        <v>1713928796</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -11797,6 +12299,7 @@
         </is>
       </c>
       <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11815,7 +12318,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1711163403</v>
+        <v>1713928834</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -11829,6 +12332,7 @@
         </is>
       </c>
       <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11847,7 +12351,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1711163439</v>
+        <v>1713928862</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -11861,6 +12365,7 @@
         </is>
       </c>
       <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -11879,7 +12384,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1711163466</v>
+        <v>1713928898</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -11893,6 +12398,7 @@
         </is>
       </c>
       <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11911,7 +12417,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1711163507</v>
+        <v>1713928930</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -11925,6 +12431,7 @@
         </is>
       </c>
       <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11943,7 +12450,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1711163537</v>
+        <v>1713928964</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -11957,6 +12464,11 @@
         </is>
       </c>
       <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -11975,7 +12487,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1711238348</v>
+        <v>1714004151</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -11989,6 +12501,7 @@
         </is>
       </c>
       <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12007,7 +12520,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>1711238372</v>
+        <v>1714004179</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -12021,6 +12534,7 @@
         </is>
       </c>
       <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12039,7 +12553,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1711238399</v>
+        <v>1714004214</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -12053,6 +12567,7 @@
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12071,7 +12586,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1711238433</v>
+        <v>1714004243</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -12085,6 +12600,7 @@
         </is>
       </c>
       <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12103,7 +12619,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1711238470</v>
+        <v>1714004263</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -12117,6 +12633,7 @@
         </is>
       </c>
       <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12135,7 +12652,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1711238505</v>
+        <v>1714004284</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -12149,6 +12666,7 @@
         </is>
       </c>
       <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12167,7 +12685,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1711242871</v>
+        <v>1714006957</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -12181,6 +12699,7 @@
         </is>
       </c>
       <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12199,7 +12718,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1711242897</v>
+        <v>1714006978</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -12213,6 +12732,7 @@
         </is>
       </c>
       <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12231,7 +12751,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1711242931</v>
+        <v>1714007005</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -12245,6 +12765,7 @@
         </is>
       </c>
       <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12263,7 +12784,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1711242970</v>
+        <v>1714007036</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -12277,6 +12798,7 @@
         </is>
       </c>
       <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12295,7 +12817,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1711243008</v>
+        <v>1714007063</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -12309,6 +12831,7 @@
         </is>
       </c>
       <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12327,7 +12850,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1711243029</v>
+        <v>1714007092</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -12341,6 +12864,11 @@
         </is>
       </c>
       <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12359,7 +12887,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1711244522</v>
+        <v>1714010951</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -12373,6 +12901,7 @@
         </is>
       </c>
       <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -12391,7 +12920,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1711244545</v>
+        <v>1714010986</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -12405,6 +12934,7 @@
         </is>
       </c>
       <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12423,7 +12953,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1711244573</v>
+        <v>1714011039</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -12437,6 +12967,7 @@
         </is>
       </c>
       <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -12455,7 +12986,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1711246133</v>
+        <v>1714011072</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -12469,6 +13000,7 @@
         </is>
       </c>
       <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12487,7 +13019,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1711246166</v>
+        <v>1714011115</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -12501,6 +13033,7 @@
         </is>
       </c>
       <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -12519,7 +13052,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1711246195</v>
+        <v>1714011143</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -12533,6 +13066,11 @@
         </is>
       </c>
       <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -12551,7 +13089,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1711250873</v>
+        <v>1714088686</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -12565,6 +13103,7 @@
         </is>
       </c>
       <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12583,7 +13122,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1711250902</v>
+        <v>1714088724</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -12597,6 +13136,7 @@
         </is>
       </c>
       <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -12615,7 +13155,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1711250931</v>
+        <v>1714088752</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -12629,6 +13169,7 @@
         </is>
       </c>
       <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -12647,7 +13188,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1711250965</v>
+        <v>1714088789</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -12661,6 +13202,7 @@
         </is>
       </c>
       <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -12679,7 +13221,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1711251002</v>
+        <v>1714088824</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -12693,6 +13235,7 @@
         </is>
       </c>
       <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -12711,7 +13254,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1711251036</v>
+        <v>1714088851</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -12725,6 +13268,7 @@
         </is>
       </c>
       <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -12743,7 +13287,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1711326208</v>
+        <v>1714090790</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -12757,6 +13301,7 @@
         </is>
       </c>
       <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -12775,7 +13320,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1711326235</v>
+        <v>1714090823</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -12789,6 +13334,7 @@
         </is>
       </c>
       <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -12807,7 +13353,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1711326292</v>
+        <v>1714090855</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -12821,6 +13367,7 @@
         </is>
       </c>
       <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -12839,7 +13386,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1711326327</v>
+        <v>1714090898</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -12853,6 +13400,7 @@
         </is>
       </c>
       <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12871,7 +13419,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1711326363</v>
+        <v>1714090925</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -12885,6 +13433,7 @@
         </is>
       </c>
       <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -12903,7 +13452,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1711326399</v>
+        <v>1714090959</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -12917,6 +13466,11 @@
         </is>
       </c>
       <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -12935,7 +13489,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1711328848</v>
+        <v>1714095490</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -12949,6 +13503,7 @@
         </is>
       </c>
       <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -12967,7 +13522,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1711328870</v>
+        <v>1714095519</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -12981,6 +13536,7 @@
         </is>
       </c>
       <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -12999,7 +13555,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1711328903</v>
+        <v>1714095553</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -13013,6 +13569,7 @@
         </is>
       </c>
       <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13031,7 +13588,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1711328945</v>
+        <v>1714095585</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -13045,6 +13602,7 @@
         </is>
       </c>
       <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13063,7 +13621,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1711328991</v>
+        <v>1714095616</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -13077,6 +13635,7 @@
         </is>
       </c>
       <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13095,7 +13654,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1711329030</v>
+        <v>1714095659</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -13109,6 +13668,7 @@
         </is>
       </c>
       <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13127,7 +13687,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1711335980</v>
+        <v>1714098565</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -13141,6 +13701,7 @@
         </is>
       </c>
       <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13159,7 +13720,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1711336017</v>
+        <v>1714098609</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -13173,6 +13734,7 @@
         </is>
       </c>
       <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -13191,7 +13753,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1711336056</v>
+        <v>1714098634</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -13205,6 +13767,7 @@
         </is>
       </c>
       <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -13223,7 +13786,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1711336075</v>
+        <v>1714098667</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -13237,6 +13800,7 @@
         </is>
       </c>
       <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -13255,7 +13819,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1711336109</v>
+        <v>1714098704</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -13269,6 +13833,7 @@
         </is>
       </c>
       <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -13287,7 +13852,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1711336152</v>
+        <v>1714098736</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -13301,774 +13866,11 @@
         </is>
       </c>
       <c r="H402" t="inlineStr"/>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D403" t="n">
-        <v>1711413235</v>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr"/>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D404" t="n">
-        <v>1711413265</v>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
-        </is>
-      </c>
-      <c r="H404" t="inlineStr"/>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D405" t="n">
-        <v>1711413286</v>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
-        </is>
-      </c>
-      <c r="H405" t="inlineStr"/>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D406" t="n">
-        <v>1711413579</v>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
-        </is>
-      </c>
-      <c r="H406" t="inlineStr"/>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D407" t="n">
-        <v>1711413605</v>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
-        </is>
-      </c>
-      <c r="H407" t="inlineStr"/>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D408" t="n">
-        <v>1711413638</v>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
-        </is>
-      </c>
-      <c r="H408" t="inlineStr"/>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D409" t="n">
-        <v>1711415897</v>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
-        </is>
-      </c>
-      <c r="H409" t="inlineStr"/>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D410" t="n">
-        <v>1711415925</v>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
-        </is>
-      </c>
-      <c r="H410" t="inlineStr"/>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D411" t="n">
-        <v>1711415952</v>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
-        </is>
-      </c>
-      <c r="H411" t="inlineStr"/>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D412" t="n">
-        <v>1711415981</v>
-      </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr"/>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D413" t="n">
-        <v>1711416010</v>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr"/>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D414" t="n">
-        <v>1711416061</v>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
-        </is>
-      </c>
-      <c r="H414" t="inlineStr"/>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D415" t="n">
-        <v>1711418755</v>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr"/>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D416" t="n">
-        <v>1711418776</v>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D417" t="n">
-        <v>1711418816</v>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
-        </is>
-      </c>
-      <c r="H417" t="inlineStr"/>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D418" t="n">
-        <v>1711418875</v>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
-        </is>
-      </c>
-      <c r="H418" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D419" t="n">
-        <v>1711418919</v>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
-        </is>
-      </c>
-      <c r="H419" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D420" t="n">
-        <v>1711418956</v>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
-        </is>
-      </c>
-      <c r="H420" t="inlineStr"/>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D421" t="n">
-        <v>1711421699</v>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
-        </is>
-      </c>
-      <c r="H421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D422" t="n">
-        <v>1711421750</v>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
-        </is>
-      </c>
-      <c r="H422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D423" t="n">
-        <v>1711421787</v>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dark</t>
-        </is>
-      </c>
-      <c r="H423" t="inlineStr"/>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D424" t="n">
-        <v>1711421826</v>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: Dim</t>
-        </is>
-      </c>
-      <c r="H424" t="inlineStr"/>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D425" t="n">
-        <v>1711421868</v>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ComfortableBrightness</t>
-        </is>
-      </c>
-      <c r="H425" t="inlineStr"/>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Brightness_Change</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D426" t="n">
-        <v>1711421897</v>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Brightness.state: ExcessivelyBright</t>
-        </is>
-      </c>
-      <c r="H426" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
